--- a/backend/media/templates/dealership_profitability.xlsx
+++ b/backend/media/templates/dealership_profitability.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AgingAndLease" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AgingAndLease" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +55,8 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -70,13 +71,28 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -96,7 +112,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -127,12 +143,6 @@
         <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004B5563"/>
-        <bgColor rgb="004B5563"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -160,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,41 +187,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -577,6 +593,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>INTERNAL FINANCE TRAINING: LEASING COST MARKUP MATRIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Instructions: Fill in the empty highlighted cells using the requested Excel functions. Do NOT hardcode values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Score Tier</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Base Provision (%)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Premium Markup (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Tier B</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Tier C</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -586,336 +701,291 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>INTERNAL FINANCE TRAINING: DEALERSHIP PROFITABILITY &amp; CAPITAL EVALUATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Instructions: Fill in the empty highlighted cells using the requested Excel functions. Do NOT hardcode values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>VIN</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Days in Stock</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Aging Bracket (0-30 days, 31-90 days, 90+ days)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Daily Holding Cost (AED)</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>INTERNAL FINANCE TRAINING: ADVANCED CAPITAL BUDGETING &amp; AGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Receipt Date</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Base Cost (AED)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Aging Bracket</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Compounding Penalty</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>LC2001</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Land Cruiser</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
+      <c r="A5" s="10" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>450000</v>
+      </c>
+      <c r="C5" s="12">
+        <f>TODAY()-A5</f>
+        <v/>
+      </c>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>LC2002</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Land Cruiser</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
+      <c r="A6" s="10" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C6" s="12">
+        <f>TODAY()-A6</f>
+        <v/>
+      </c>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>RAV2001</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>RAV4</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
+      <c r="A7" s="10" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>85000</v>
+      </c>
+      <c r="C7" s="12">
+        <f>TODAY()-A7</f>
+        <v/>
+      </c>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Section 2: Branch Performance Matrix (Lookup Sheet)</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Capital Project Analysis Dashboard:</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>Formula Guidelines:</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Units Sold</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Net Profit (AED)</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>CSAT Score</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Score Tier</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Base Provision (%)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Premium Markup (%)</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>D5-D7: Aging Bracket. If days &lt;= 30: '0-30 days', if days &lt;= 90: '31-90 days', else: '90+ days'</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>150</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Tier A</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>E5-E7: Holding Cost. If bracket is '0-30 days': 50, if '31-90 days': 100, else: 150 (use Nested IF)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Abu Dhabi</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>4.7</v>
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Tier B</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Sharjah</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Tier C</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>B17: 2D query based on B15 and B16 from mini performance matrix (use INDEX/MATCH)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Perform 2D Matrix Query here:</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Query Branch:</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Select Tier:</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Tier B</t>
+        </is>
+      </c>
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>F21: Calculate XNPV on lease cash flows given discount rate (r) in D21 (use XNPV)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Query Metric:</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Net Profit (AED)</t>
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>Select Metric:</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Premium Markup (%)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Extracted Performance Metric:</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n"/>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Resulting Allocation:</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n"/>
+      <c r="H17" s="17" t="inlineStr">
         <is>
           <t>F23: Calculate XIRR on lease cash flows (use XIRR)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Section 3: Lease Capital Finance Processing</t>
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Showroom Leasing Capital Project flows:</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Cash Flow Date</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Amount (AED)</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Project Date</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Cash Flow (AED)</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Discount Rate (r)</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Required Calculations:</t>
-        </is>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="D21" s="21" t="n">
+      <c r="A21" s="24" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="D21" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>Project XNPV (AED):</t>
         </is>
       </c>
-      <c r="F21" s="19" t="n"/>
+      <c r="F21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>250000</v>
+      <c r="A22" s="24" t="n">
+        <v>46534</v>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n">
-        <v>46387</v>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="A23" s="24" t="n">
+        <v>46900</v>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>Project XIRR (%):</t>
         </is>
       </c>
-      <c r="F23" s="19" t="n"/>
+      <c r="F23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
-        <v>46568</v>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>300000</v>
+      <c r="A24" s="24" t="n">
+        <v>47265</v>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>150000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n">
-        <v>46752</v>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>350000</v>
+      <c r="A25" s="24" t="n">
+        <v>47630</v>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>180000</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
